--- a/Paper/_output/_comparison/crisis_analysis_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_yearly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -454,8 +454,11 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,12 +544,27 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>hit_count_full</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>hit_rate_ptt</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ptt</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ttp</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ttp</t>
         </is>
       </c>
     </row>
@@ -603,8 +621,11 @@
         <v>0.1601355097176136</v>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -661,11 +682,26 @@
       <c r="P3" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -723,11 +759,26 @@
       <c r="P4" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n">
         <v>0.1666666666666667</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1/6</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -785,11 +836,26 @@
       <c r="P5" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n">
         <v>0.1666666666666667</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1/6</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -847,11 +913,26 @@
       <c r="P6" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -909,11 +990,26 @@
       <c r="P7" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -971,11 +1067,26 @@
       <c r="P8" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q8" s="2" t="n">
-        <v>0.5</v>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
       <c r="R8" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Paper/_output/_comparison/crisis_analysis_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_yearly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,12 +784,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10.80090714919682</v>
+        <v>9.100240007027905</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.2726456276515822</v>
+        <v>-0.3774670338474645</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.4019616742567396</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1083264094538176</v>
+        <v>0.08991080425787042</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1719022327527441</v>
+        <v>0.1643299012213698</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9058506106219824</v>
+        <v>0.9120988355580801</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.09234242500001333</v>
+        <v>0.08627628706692314</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3917996886074401</v>
+        <v>0.3759620822245726</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5494835175753592</v>
+        <v>0.5269644188142332</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.1984851309090535</v>
+        <v>0.21463809261531</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3840428795918789</v>
+        <v>0.3663698603541443</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
@@ -861,12 +861,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -875,75 +875,75 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20.76996724011253</v>
+        <v>10.80090714919682</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.3418020036752321</v>
+        <v>-0.2726456276515822</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1796651088430173</v>
+        <v>0.1083264094538176</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2074186252950895</v>
+        <v>0.1719022327527441</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9139449020164726</v>
+        <v>0.9058506106219824</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1165434447742071</v>
+        <v>0.09234242500001333</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4303670334458785</v>
+        <v>0.3917996886074401</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.6068911799117904</v>
+        <v>0.5494835175753592</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.2250348376385347</v>
+        <v>0.1984851309090535</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.6701720817343015</v>
+        <v>0.3840428795918789</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -952,138 +952,215 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18.26885844762476</v>
+        <v>20.76996724011253</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1876450060024839</v>
+        <v>0.3418020036752321</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1944571633105226</v>
+        <v>0.1796651088430173</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2108371930112495</v>
+        <v>0.2074186252950895</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9187730758307299</v>
+        <v>0.9139449020164726</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1116778227562685</v>
+        <v>0.1165434447742071</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4026733039244095</v>
+        <v>0.4303670334458785</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.5663859966725959</v>
+        <v>0.6068911799117904</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.2085560048256974</v>
+        <v>0.2250348376385347</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.6616703820773265</v>
+        <v>0.6701720817343015</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>18.26885844762476</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.1876450060024839</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.5354812145044887</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1944571633105226</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2108371930112495</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9187730758307299</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.1116778227562685</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.4026733039244095</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.5663859966725959</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0.2085560048256974</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.6616703820773265</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>19.92202128053735</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.2895384621173984</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.4876150815614988</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1587171316326844</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.2020815790601596</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9113888099971599</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>0.1149571628825923</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>0.4346939649526406</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.6118260969946161</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N9" s="3" t="n">
         <v>0.2357539117011369</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.7090015670332926</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
       </c>
-      <c r="T8" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1100,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1404,12 +1481,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1418,60 +1495,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.4355826533357545</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.5835345717831015</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.3043384976802425</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.0881793893681919</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.1489104471765209</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9462603878116344</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.1452528993287905</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.6141277895968544</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.3087473051992134</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.3043384976802425</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.6795408281682738</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.01895340505933174</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.9544262269956552</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.1145536846800933</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1480,60 +1557,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.0885112574001572</v>
+        <v>0.2778810924357364</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.005427261428731622</v>
+        <v>0.409580203409349</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2850465641718551</v>
+        <v>0.1114259070568875</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1968916734512504</v>
+        <v>0.1527123066850303</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9584487534626038</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.5046718081597295</v>
+        <v>-0.2517736539689071</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.06460870262993701</v>
+        <v>0.412971084767529</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.072722551490211</v>
+        <v>0.5351661656481069</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8401713401642454</v>
+        <v>0.7078803749883373</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.07487343987011807</v>
+        <v>-0.002399823602007745</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.180034412920183</v>
+        <v>0.9942295848294278</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1423032147182204</v>
+        <v>-0.1157994371504594</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1542,19 +1619,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.1051693667903664</v>
+        <v>-0.0885112574001572</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.01294764165236018</v>
+        <v>0.005427261428731622</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.3008863680359475</v>
+        <v>0.2850465641718551</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1971883490136813</v>
+        <v>0.1968916734512504</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0.9988919667590028</v>
@@ -1563,39 +1640,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5165540962256934</v>
+        <v>-0.5046718081597295</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.08704754021851291</v>
+        <v>-0.06460870262993701</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.097979358321054</v>
+        <v>1.072722551490211</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8509426312718931</v>
+        <v>0.8401713401642454</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.08116512286290178</v>
+        <v>0.07487343987011807</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.195162867761455</v>
+        <v>1.180034412920183</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1452618683874185</v>
+        <v>-0.1423032147182204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1604,48 +1681,110 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.02359204792244729</v>
+        <v>-0.1051693667903664</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.07703707946457228</v>
+        <v>-0.01294764165236018</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.2543247912284557</v>
+        <v>0.3008863680359475</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1824361712833101</v>
+        <v>0.1971883490136813</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.997229916897507</v>
+        <v>0.9988919667590028</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>-0.5165540962256934</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.08704754021851291</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.097979358321054</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.522337027033672</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.8509426312718931</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.08116512286290178</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.195162867761455</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1452618683874185</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.02359204792244729</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.07703707946457228</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-0.4876150815614987</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.2543247912284557</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.1824361712833101</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.997229916897507</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.4816886905342951</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-0.0212067550577778</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.023869993883996</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.4876150815614987</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.8838252884816873</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.1003724075845553</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.241347098573505</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.1388121261286483</v>
       </c>
     </row>
@@ -1660,7 +1799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1964,12 +2103,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1978,60 +2117,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.1975871140978549</v>
+        <v>0.3499625568620768</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1368616548924535</v>
+        <v>0.2815106712242617</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.4019616742567399</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1847647558521955</v>
+        <v>0.1399665328165783</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2118271660599822</v>
+        <v>0.1982343541210623</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9614825581395349</v>
+        <v>0.936046511627907</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.4019616742567399</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07708757922255405</v>
+        <v>0.2045306567846077</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.9239869583598836</v>
+        <v>0.7983203326963466</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.4019616742567399</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.239468393809461</v>
+        <v>1.257317798460998</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.05549602170052359</v>
+        <v>0.0639087216303369</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.104970005642202</v>
+        <v>1.120882518504188</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1172405796580748</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2040,60 +2179,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1019213862233868</v>
+        <v>0.1975871140978549</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.04604680190383625</v>
+        <v>0.1368616548924535</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2007330591320373</v>
+        <v>0.1847647558521955</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2406643520933329</v>
+        <v>0.2118271660599822</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9738372093023255</v>
+        <v>0.9614825581395349</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.5031043706109168</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0008154879999826559</v>
+        <v>0.07708757922255405</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9991958792334011</v>
+        <v>0.9239869583598836</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.217611347433591</v>
+        <v>1.239468393809461</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.04519445836539138</v>
+        <v>0.05549602170052359</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.085484732134711</v>
+        <v>1.104970005642202</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1903416370175206</v>
+        <v>-0.1247701957278803</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2102,110 +2241,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.0368407257795742</v>
+        <v>0.1019213862233868</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.01573384558532909</v>
+        <v>0.04604680190383625</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2138025395451635</v>
+        <v>0.2007330591320373</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2486051666650726</v>
+        <v>0.2406643520933329</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9898255813953488</v>
+        <v>0.9738372093023255</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5129198176356869</v>
+        <v>-0.5031043706109168</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.01895415943304257</v>
+        <v>0.0008154879999826559</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.018689954007736</v>
+        <v>0.9991958792334011</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.128685919321732</v>
+        <v>1.217611347433591</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.003282531472589278</v>
+        <v>0.04519445836539138</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.006208865728391</v>
+        <v>1.085484732134711</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.204891821182839</v>
+        <v>-0.1903416370175206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.0368407257795742</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-0.01573384558532909</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.514605350956002</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.2138025395451635</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2486051666650726</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9898255813953488</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.5129198176356869</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.01895415943304257</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.018689954007736</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.514605350956002</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1.128685919321732</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.003282531472589278</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.006208865728391</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.204891821182839</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.1822704228151848</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.1223216195212393</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.4718154607749649</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1693242986572223</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.2376559716880013</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9636627906976745</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.4706028507084905</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.06627797665555812</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.9346458839393986</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.4718154607749649</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>1.233239118112769</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.05256006791162027</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.099416687109758</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.1671095976979867</v>
       </c>
     </row>
@@ -2220,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2524,12 +2725,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2538,60 +2739,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>0.004205705299217932</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>-0.01876488188421255</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1434541510678393</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.04678097528829382</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.1552469470901619</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9862068965517241</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.138687252248779</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.07053469759807562</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.7096268615961698</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1434541510678393</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>0.1659013615217844</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>-0.08341586655962385</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>0.6099159566998359</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.02192041710993009</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2600,60 +2801,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.05429070103913802</v>
+        <v>0.01678534845024493</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.03017445041727607</v>
+        <v>-0.006472990324530081</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.05847802996069337</v>
+        <v>0.04633586591900118</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1943365262252255</v>
+        <v>0.1676448275252702</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.9517241379310345</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0327416689383877</v>
+        <v>0.06089581754970363</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.8652110026700077</v>
+        <v>0.7493076420581847</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2688449302478968</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.002485828352167374</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9883753293641022</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02892173456683256</v>
+        <v>-0.02330447460112972</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2662,110 +2863,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.05350828208151159</v>
+        <v>0.05429070103913802</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.02940992881154214</v>
+        <v>0.03017445041727607</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.1775169494986034</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.06099826392968127</v>
+        <v>0.05847802996069337</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1970235800584944</v>
+        <v>0.1943365262252255</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.1690941297033365</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>0.0327416689383877</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.8984331176243276</v>
+        <v>0.8652110026700077</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.1775169494986034</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2778889047779733</v>
+        <v>0.2688449302478968</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.004624175830937105</v>
+        <v>-0.002485828352167374</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.021624389692979</v>
+        <v>0.9883753293641022</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02931693909409494</v>
+        <v>-0.02892173456683256</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.05350828208151159</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.02940992881154214</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.1829503201425123</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.06099826392968127</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.1970235800584944</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.8689655172413793</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.1755869558437451</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.02467166685502487</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.8984331176243276</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.1829503201425123</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.2778889047779733</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.004624175830937105</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.021624389692979</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.02931693909409494</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.03061996343987849</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.007045166365681865</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.1652260547018463</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.05187138456619264</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1829382024919134</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.903448275862069</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.163574613865239</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.03960193338246176</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.8369690652301233</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.1652260547018463</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.2321720269664671</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.03131657028652601</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.8535519096845917</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.02321227998309094</v>
       </c>
     </row>
@@ -2780,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3084,12 +3347,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3098,19 +3361,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.001560322013030691</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.08768794751503295</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422493289217</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.1125125693043114</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.4092856064157859</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -3119,39 +3382,39 @@
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422493289217</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.007998764021966531</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.9804376909420194</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422493289217</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.3998874441902356</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.09492740958848467</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7314395722407911</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.08260648781657542</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3160,60 +3423,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>0.003752373695923961</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>-0.0856912278706744</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.4277127620168583</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9918032786885246</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.02953137989967969</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.072223905958428</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.4142266877546186</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.08565662401838847</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.7576676780024697</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>-0.07121447292125116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3222,19 +3485,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>0.03488923518577902</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>-0.05732894814631817</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.1241006863166954</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4741154654082622</v>
+        <v>0.4729976975805062</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0.9590163934426229</v>
@@ -3243,89 +3506,151 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>-0.02953137989967969</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>1.072223905958428</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.502409700880692</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>-0.02864344881523828</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>0.9189644287180407</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>-0.06316869981712403</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.03395357056649728</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>-0.05818123641143114</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1251027258735238</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.4741154654082622</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9590163934426229</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.3121003427249628</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.03082746164398775</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.075393689637123</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.5030587086818397</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>-0.02822384424329949</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.9201515377292117</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.06371665664689741</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.04515891089417345</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>-0.04797439533710812</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.3019274392708716</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1195047161892575</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.4584419203783911</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9508196721311475</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.3019274392708716</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-0.01649499533326504</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.040341257190876</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.3019274392708716</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.4972066941042887</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.03200736127876636</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.9094475381374805</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.06227097997115527</v>
       </c>
     </row>
@@ -3340,7 +3665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3644,12 +3969,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3658,60 +3983,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.09480060127513035</v>
+        <v>0.01404474995820859</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.03184073837926271</v>
+        <v>-0.04427100028277864</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1155318330023982</v>
+        <v>0.1240394247573673</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1720647483703307</v>
+        <v>0.1633727596186971</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4372788934221374</v>
+        <v>0.3142505667229638</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.06508110111248899</v>
+        <v>-0.1451083722677065</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.813799478447114</v>
+        <v>0.5848371626159791</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.08922573857760219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3720,60 +4045,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3595704026356366</v>
+        <v>0.09480060127513035</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.2813841410940174</v>
+        <v>0.03184073837926271</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1392666701512926</v>
+        <v>0.1155318330023982</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2294212443587999</v>
+        <v>0.1720647483703307</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9122807017543859</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.02227482471563635</v>
+        <v>0.1036687135184475</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9503814318660629</v>
+        <v>0.769071443176754</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9269870146170396</v>
+        <v>0.4372788934221374</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.2534634621863614</v>
+        <v>-0.06508110111248899</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.725172562340744</v>
+        <v>0.813799478447114</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.111586064624036</v>
+        <v>-0.08016850348153992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3782,110 +4107,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.2930599188275502</v>
+        <v>0.3595704026356366</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.2186985464363551</v>
+        <v>0.2813841410940174</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1617038815488626</v>
+        <v>0.1392666701512926</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.244271120885344</v>
+        <v>0.2294212443587999</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9317738791423001</v>
+        <v>0.9122807017543859</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3268135676014445</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.02460593955894141</v>
+        <v>0.02227482471563635</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.054811272550568</v>
+        <v>0.9503814318660629</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9208050795385059</v>
+        <v>0.9269870146170396</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.2494422468446016</v>
+        <v>0.2534634621863614</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.713667649530219</v>
+        <v>1.725172562340744</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1128970535188779</v>
+        <v>-0.111586064624036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.2930599188275502</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.2186985464363551</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1617038815488626</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.244271120885344</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9317738791423001</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.3268135676014445</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.02460593955894141</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.054811272550568</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.9208050795385059</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.2494422468446016</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.713667649530219</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1128970535188779</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.265288122701582</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.1925238525356017</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.324043264289569</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1660049019432621</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.2482386617226885</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9259259259259259</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.3240432642895691</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-0.02059198849579269</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.045869944982081</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.324043264289569</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.8718477912225604</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.2175965874570334</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.622555509664736</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.11030602040881</v>
       </c>
     </row>
@@ -3900,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4204,12 +4591,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4218,19 +4605,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.02335558522365555</v>
+        <v>-0.05944967618015007</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.02100989850384682</v>
+        <v>-0.05719067958884594</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.07028481312061448</v>
+        <v>0.0679413098331703</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.2181663348217244</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4239,39 +4626,39 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1277711346285673</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.6940712220239806</v>
+        <v>0.5578762400716401</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.07500868839622021</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.1640065156290161</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.2623547528124305</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.04964464462786422</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4280,19 +4667,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.02506240001890081</v>
+        <v>-0.02335558522365555</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.02272081269569726</v>
+        <v>-0.02100989850384682</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1047999997493329</v>
+        <v>0.07028481312061448</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.3040021784991731</v>
+        <v>0.2368473235282732</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4301,39 +4688,39 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.02546035277715153</v>
+        <v>0.08841159562168954</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.91190007874893</v>
+        <v>0.6940712220239806</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2254874204614814</v>
+        <v>0.1566293869752668</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.04698491301235053</v>
+        <v>-0.1005331940285291</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7886779214828342</v>
+        <v>0.5478360571510722</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.07692212197636894</v>
+        <v>-0.04423229897254077</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4342,19 +4729,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.01474881982114307</v>
+        <v>-0.02506240001890081</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.01238246152936839</v>
+        <v>-0.02272081269569726</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.103867108384541</v>
+        <v>0.1047999997493329</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3059568480665255</v>
+        <v>0.3040021784991731</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -4363,39 +4750,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2083486754324957</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.02043384461706754</v>
+        <v>0.02546035277715153</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.9292931988265379</v>
+        <v>0.91190007874893</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2445519253278838</v>
+        <v>0.2254874204614814</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.0321591706503529</v>
+        <v>-0.04698491301235053</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8553590429456704</v>
+        <v>0.7886779214828342</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.07255193694871198</v>
+        <v>-0.07692212197636894</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4404,19 +4791,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.02466362643383457</v>
+        <v>-0.01474881982114307</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.02232108134351685</v>
+        <v>-0.01238246152936839</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1878863304044792</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.09228250964986333</v>
+        <v>0.103867108384541</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2759947934484516</v>
+        <v>0.3059568480665255</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -4425,27 +4812,89 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>-0.2083486754324957</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.02043384461706754</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.9292931988265379</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.2445519253278838</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>-0.0321591706503529</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.8553590429456704</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.07255193694871198</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.02466362643383457</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>-0.02232108134351685</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>-0.1878863304044792</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="G9" s="2" t="n">
+        <v>0.09228250964986333</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.2759947934484516</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>0.04680968554454545</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.8380254332546916</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.1878863304044792</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.2009850468985936</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.06603947961381429</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.702976994072228</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.05694989141396378</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_yearly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,12 +784,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9.100240007027905</v>
+        <v>10.80090714919682</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.3774670338474645</v>
+        <v>-0.2726456276515822</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.08991080425787042</v>
+        <v>0.1083264094538176</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1643299012213698</v>
+        <v>0.1719022327527441</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9120988355580801</v>
+        <v>0.9058506106219824</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.08627628706692314</v>
+        <v>0.09234242500001333</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3759620822245726</v>
+        <v>0.3917996886074401</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5269644188142332</v>
+        <v>0.5494835175753592</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.21463809261531</v>
+        <v>0.1984851309090535</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3663698603541443</v>
+        <v>0.3840428795918789</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
@@ -861,12 +861,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -875,75 +875,75 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10.80090714919682</v>
+        <v>20.76996724011253</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.2726456276515822</v>
+        <v>0.3418020036752321</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1083264094538176</v>
+        <v>0.1796651088430173</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1719022327527441</v>
+        <v>0.2074186252950895</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9058506106219824</v>
+        <v>0.9139449020164726</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.09234242500001333</v>
+        <v>0.1165434447742071</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.3917996886074401</v>
+        <v>0.4303670334458785</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.5494835175753592</v>
+        <v>0.6068911799117904</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.1984851309090535</v>
+        <v>0.2250348376385347</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.3840428795918789</v>
+        <v>0.6701720817343015</v>
       </c>
       <c r="P6" s="2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>3/6</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -952,75 +952,75 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>20.76996724011253</v>
+        <v>18.26885844762476</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.3418020036752321</v>
+        <v>0.1876450060024839</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1796651088430173</v>
+        <v>0.1944571633105226</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2074186252950895</v>
+        <v>0.2108371930112495</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9139449020164726</v>
+        <v>0.9187730758307299</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1165434447742071</v>
+        <v>0.1116778227562685</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4303670334458785</v>
+        <v>0.4026733039244095</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.6068911799117904</v>
+        <v>0.5663859966725959</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.2250348376385347</v>
+        <v>0.2085560048256974</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.6701720817343015</v>
+        <v>0.6616703820773265</v>
       </c>
       <c r="P7" s="2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1029,138 +1029,61 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>18.26885844762476</v>
+        <v>19.92202128053735</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1876450060024839</v>
+        <v>0.2895384621173984</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1944571633105226</v>
+        <v>0.1587171316326844</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2108371930112495</v>
+        <v>0.2020815790601596</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9187730758307299</v>
+        <v>0.9113888099971599</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1116778227562685</v>
+        <v>0.1149571628825923</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4026733039244095</v>
+        <v>0.4346939649526406</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.5663859966725959</v>
+        <v>0.6118260969946161</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.2085560048256974</v>
+        <v>0.2357539117011369</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.6616703820773265</v>
+        <v>0.7090015670332926</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U8" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>19.92202128053735</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.2895384621173984</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.4876150815614988</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1587171316326844</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2020815790601596</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9113888099971599</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.1149571628825923</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.4346939649526406</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.6118260969946161</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.2357539117011369</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.7090015670332926</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1177,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1481,12 +1404,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1495,60 +1418,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4355826533357545</v>
+        <v>0.2778810924357364</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5835345717831015</v>
+        <v>0.409580203409349</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0881793893681919</v>
+        <v>0.1114259070568875</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1489104471765209</v>
+        <v>0.1527123066850303</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9462603878116344</v>
+        <v>0.9584487534626038</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1452528993287905</v>
+        <v>-0.2517736539689071</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.6141277895968544</v>
+        <v>0.412971084767529</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.3087473051992134</v>
+        <v>0.5351661656481069</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.6795408281682738</v>
+        <v>0.7078803749883373</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.01895340505933174</v>
+        <v>-0.002399823602007745</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.9544262269956552</v>
+        <v>0.9942295848294278</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1145536846800933</v>
+        <v>-0.1157994371504594</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1557,60 +1480,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>-0.0885112574001572</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.005427261428731622</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.2850465641718551</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.1968916734512504</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9988919667590028</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.5046718081597295</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>-0.06460870262993701</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>1.072722551490211</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.8401713401642454</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>0.07487343987011807</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>1.180034412920183</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.1423032147182204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1619,19 +1542,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.0885112574001572</v>
+        <v>-0.1051693667903664</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.005427261428731622</v>
+        <v>-0.01294764165236018</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2850465641718551</v>
+        <v>0.3008863680359475</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1968916734512504</v>
+        <v>0.1971883490136813</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0.9988919667590028</v>
@@ -1640,39 +1563,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5046718081597295</v>
+        <v>-0.5165540962256934</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.06460870262993701</v>
+        <v>-0.08704754021851291</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.072722551490211</v>
+        <v>1.097979358321054</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8401713401642454</v>
+        <v>0.8509426312718931</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.07487343987011807</v>
+        <v>0.08116512286290178</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.180034412920183</v>
+        <v>1.195162867761455</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1423032147182204</v>
+        <v>-0.1452618683874185</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1681,110 +1604,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.1051693667903664</v>
+        <v>-0.02359204792244729</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.01294764165236018</v>
+        <v>0.07703707946457228</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.4876150815614987</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.3008863680359475</v>
+        <v>0.2543247912284557</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1971883490136813</v>
+        <v>0.1824361712833101</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.997229916897507</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5165540962256934</v>
+        <v>-0.4816886905342951</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.08704754021851291</v>
+        <v>-0.0212067550577778</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.097979358321054</v>
+        <v>1.023869993883996</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.4876150815614987</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.8509426312718931</v>
+        <v>0.8838252884816873</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.08116512286290178</v>
+        <v>0.1003724075845553</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.195162867761455</v>
+        <v>1.241347098573505</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1452618683874185</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>-0.02359204792244729</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.07703707946457228</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.4876150815614987</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.2543247912284557</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.1824361712833101</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.997229916897507</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.4816886905342951</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.0212067550577778</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.023869993883996</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.4876150815614987</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.8838252884816873</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.1003724075845553</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.241347098573505</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.1388121261286483</v>
       </c>
     </row>
@@ -1799,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2103,12 +1964,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2117,60 +1978,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3499625568620768</v>
+        <v>0.1975871140978549</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.2815106712242617</v>
+        <v>0.1368616548924535</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1399665328165783</v>
+        <v>0.1847647558521955</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1982343541210623</v>
+        <v>0.2118271660599822</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.936046511627907</v>
+        <v>0.9614825581395349</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.2045306567846077</v>
+        <v>0.07708757922255405</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7983203326963466</v>
+        <v>0.9239869583598836</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.257317798460998</v>
+        <v>1.239468393809461</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.0639087216303369</v>
+        <v>0.05549602170052359</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.120882518504188</v>
+        <v>1.104970005642202</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1172405796580748</v>
+        <v>-0.1247701957278803</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2179,60 +2040,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1975871140978549</v>
+        <v>0.1019213862233868</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.1368616548924535</v>
+        <v>0.04604680190383625</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1847647558521955</v>
+        <v>0.2007330591320373</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2118271660599822</v>
+        <v>0.2406643520933329</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9614825581395349</v>
+        <v>0.9738372093023255</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.5031043706109168</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.07708757922255405</v>
+        <v>0.0008154879999826559</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9239869583598836</v>
+        <v>0.9991958792334011</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.239468393809461</v>
+        <v>1.217611347433591</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.05549602170052359</v>
+        <v>0.04519445836539138</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.104970005642202</v>
+        <v>1.085484732134711</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1903416370175206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2241,60 +2102,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1019213862233868</v>
+        <v>0.0368407257795742</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.04604680190383625</v>
+        <v>-0.01573384558532909</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2007330591320373</v>
+        <v>0.2138025395451635</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2406643520933329</v>
+        <v>0.2486051666650726</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9738372093023255</v>
+        <v>0.9898255813953488</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5031043706109168</v>
+        <v>-0.5129198176356869</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.0008154879999826559</v>
+        <v>-0.01895415943304257</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.9991958792334011</v>
+        <v>1.018689954007736</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.217611347433591</v>
+        <v>1.128685919321732</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.04519445836539138</v>
+        <v>0.003282531472589278</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.085484732134711</v>
+        <v>1.006208865728391</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1903416370175206</v>
+        <v>-0.204891821182839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2303,110 +2164,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.0368407257795742</v>
+        <v>0.1822704228151848</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.01573384558532909</v>
+        <v>0.1223216195212393</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.2138025395451635</v>
+        <v>0.1693242986572223</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2486051666650726</v>
+        <v>0.2376559716880013</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9898255813953488</v>
+        <v>0.9636627906976745</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.5129198176356869</v>
+        <v>-0.4706028507084905</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.01895415943304257</v>
+        <v>0.06627797665555812</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.018689954007736</v>
+        <v>0.9346458839393986</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.128685919321732</v>
+        <v>1.233239118112769</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.003282531472589278</v>
+        <v>0.05256006791162027</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.006208865728391</v>
+        <v>1.099416687109758</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.204891821182839</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.1822704228151848</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.1223216195212393</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.4718154607749649</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1693242986572223</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2376559716880013</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9636627906976745</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.4706028507084905</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.06627797665555812</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.9346458839393986</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.4718154607749649</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>1.233239118112769</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.05256006791162027</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.099416687109758</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.1671095976979867</v>
       </c>
     </row>
@@ -2421,7 +2220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2725,12 +2524,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2739,60 +2538,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.004205705299217932</v>
+        <v>0.01678534845024493</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.01876488188421255</v>
+        <v>-0.006472990324530081</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04678097528829382</v>
+        <v>0.04633586591900118</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1552469470901619</v>
+        <v>0.1676448275252702</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9517241379310345</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07053469759807562</v>
+        <v>0.06089581754970363</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7096268615961698</v>
+        <v>0.7493076420581847</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1659013615217844</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08341586655962385</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.6099159566998359</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02192041710993009</v>
+        <v>-0.02330447460112972</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2801,60 +2600,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>0.05429070103913802</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>0.03017445041727607</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1775169494986034</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.05847802996069337</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.1943365262252255</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.1690941297033365</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.0327416689383877</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.8652110026700077</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1775169494986034</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>0.2688449302478968</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>-0.002485828352167374</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>0.9883753293641022</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.02892173456683256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2863,60 +2662,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.05429070103913802</v>
+        <v>0.05350828208151159</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.03017445041727607</v>
+        <v>0.02940992881154214</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.1829503201425123</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.05847802996069337</v>
+        <v>0.06099826392968127</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1943365262252255</v>
+        <v>0.1970235800584944</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8689655172413793</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.1755869558437451</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.0327416689383877</v>
+        <v>0.02467166685502487</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.8652110026700077</v>
+        <v>0.8984331176243276</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.1829503201425123</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2688449302478968</v>
+        <v>0.2778889047779733</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.002485828352167374</v>
+        <v>0.004624175830937105</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9883753293641022</v>
+        <v>1.021624389692979</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02892173456683256</v>
+        <v>-0.02931693909409494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2925,110 +2724,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.05350828208151159</v>
+        <v>0.03061996343987849</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.02940992881154214</v>
+        <v>0.007045166365681865</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.1652260547018463</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.06099826392968127</v>
+        <v>0.05187138456619264</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1970235800584944</v>
+        <v>0.1829382024919134</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.903448275862069</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.163574613865239</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>0.03960193338246176</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.8984331176243276</v>
+        <v>0.8369690652301233</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.1652260547018463</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2778889047779733</v>
+        <v>0.2321720269664671</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.004624175830937105</v>
+        <v>-0.03131657028652601</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.021624389692979</v>
+        <v>0.8535519096845917</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02931693909409494</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.03061996343987849</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.007045166365681865</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.1652260547018463</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.05187138456619264</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.1829382024919134</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.903448275862069</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.163574613865239</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.03960193338246176</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.8369690652301233</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.1652260547018463</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.2321720269664671</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.03131657028652601</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.8535519096845917</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.02321227998309094</v>
       </c>
     </row>
@@ -3043,7 +2780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3347,12 +3084,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3361,19 +3098,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.001560322013030691</v>
+        <v>0.003752373695923961</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.08768794751503295</v>
+        <v>-0.0856912278706744</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1125125693043114</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4092856064157859</v>
+        <v>0.4277127620168583</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -3382,39 +3119,39 @@
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.007998764021966531</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.9804376909420194</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3998874441902356</v>
+        <v>0.4142266877546186</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.09492740958848467</v>
+        <v>-0.08565662401838847</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7314395722407911</v>
+        <v>0.7576676780024697</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.08260648781657542</v>
+        <v>-0.07121447292125116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3423,60 +3160,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.03488923518577902</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.05732894814631817</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.1241006863166954</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.4729976975805062</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9590163934426229</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>-0.02953137989967969</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>1.072223905958428</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.502409700880692</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.02864344881523828</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.9189644287180407</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.06316869981712403</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3485,19 +3222,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>0.03395357056649728</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>-0.05818123641143114</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.1251027258735238</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.4741154654082622</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0.9590163934426229</v>
@@ -3506,39 +3243,39 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.3121003427249628</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.02953137989967969</v>
+        <v>-0.03082746164398775</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.072223905958428</v>
+        <v>1.075393689637123</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.5030587086818397</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.02822384424329949</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.9201515377292117</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>-0.06371665664689741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3547,110 +3284,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>0.04515891089417345</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>-0.04797439533710812</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.1195047161892575</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4741154654082622</v>
+        <v>0.4584419203783911</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9508196721311475</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>-0.01649499533326504</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.4972066941042887</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>-0.03200736127876636</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>0.9094475381374805</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.06371665664689741</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.04515891089417345</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-0.04797439533710812</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1195047161892575</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.4584419203783911</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9508196721311475</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.01649499533326504</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.040341257190876</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.4972066941042887</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.03200736127876636</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.9094475381374805</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.06227097997115527</v>
       </c>
     </row>
@@ -3665,7 +3340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3969,12 +3644,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3983,60 +3658,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01404474995820859</v>
+        <v>0.09480060127513035</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.04427100028277864</v>
+        <v>0.03184073837926271</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1240394247573673</v>
+        <v>0.1155318330023982</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1633727596186971</v>
+        <v>0.1720647483703307</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>0.1036687135184475</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>0.769071443176754</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3142505667229638</v>
+        <v>0.4372788934221374</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1451083722677065</v>
+        <v>-0.06508110111248899</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.5848371626159791</v>
+        <v>0.813799478447114</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.08016850348153992</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4045,60 +3720,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.09480060127513035</v>
+        <v>0.3595704026356366</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.03184073837926271</v>
+        <v>0.2813841410940174</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1155318330023982</v>
+        <v>0.1392666701512926</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1720647483703307</v>
+        <v>0.2294212443587999</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9122807017543859</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>0.02227482471563635</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>0.9503814318660629</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.4372788934221374</v>
+        <v>0.9269870146170396</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.06508110111248899</v>
+        <v>0.2534634621863614</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.813799478447114</v>
+        <v>1.725172562340744</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.111586064624036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4107,60 +3782,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.3595704026356366</v>
+        <v>0.2930599188275502</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.2813841410940174</v>
+        <v>0.2186985464363551</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1392666701512926</v>
+        <v>0.1617038815488626</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2294212443587999</v>
+        <v>0.244271120885344</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9122807017543859</v>
+        <v>0.9317738791423001</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3268135676014445</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.02227482471563635</v>
+        <v>-0.02460593955894141</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.9503814318660629</v>
+        <v>1.054811272550568</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9269870146170396</v>
+        <v>0.9208050795385059</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.2534634621863614</v>
+        <v>0.2494422468446016</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.725172562340744</v>
+        <v>1.713667649530219</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.111586064624036</v>
+        <v>-0.1128970535188779</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4169,110 +3844,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.2930599188275502</v>
+        <v>0.265288122701582</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.2186985464363551</v>
+        <v>0.1925238525356017</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1617038815488626</v>
+        <v>0.1660049019432621</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.244271120885344</v>
+        <v>0.2482386617226885</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9317738791423001</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3268135676014445</v>
+        <v>-0.3240432642895691</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.02460593955894141</v>
+        <v>-0.02059198849579269</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.054811272550568</v>
+        <v>1.045869944982081</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9208050795385059</v>
+        <v>0.8718477912225604</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.2494422468446016</v>
+        <v>0.2175965874570334</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.713667649530219</v>
+        <v>1.622555509664736</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1128970535188779</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.265288122701582</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.1925238525356017</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1660049019432621</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2482386617226885</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9259259259259259</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.3240432642895691</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.02059198849579269</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.045869944982081</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.8718477912225604</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.2175965874570334</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.622555509664736</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.11030602040881</v>
       </c>
     </row>
@@ -4287,7 +3900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4591,12 +4204,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4605,19 +4218,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>-0.02335558522365555</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>-0.02100989850384682</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0.07028481312061448</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>0.2368473235282732</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4626,39 +4239,39 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.08841159562168954</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>0.6940712220239806</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.1566293869752668</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.1005331940285291</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.5478360571510722</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>-0.04423229897254077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4667,19 +4280,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.02335558522365555</v>
+        <v>-0.02506240001890081</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.02100989850384682</v>
+        <v>-0.02272081269569726</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.07028481312061448</v>
+        <v>0.1047999997493329</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.3040021784991731</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4688,39 +4301,39 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.02546035277715153</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.6940712220239806</v>
+        <v>0.91190007874893</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.2254874204614814</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.04698491301235053</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.7886779214828342</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.07692212197636894</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4729,19 +4342,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.02506240001890081</v>
+        <v>-0.01474881982114307</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.02272081269569726</v>
+        <v>-0.01238246152936839</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1047999997493329</v>
+        <v>0.103867108384541</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3040021784991731</v>
+        <v>0.3059568480665255</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -4750,39 +4363,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2083486754324957</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.02546035277715153</v>
+        <v>0.02043384461706754</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.91190007874893</v>
+        <v>0.9292931988265379</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2254874204614814</v>
+        <v>0.2445519253278838</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.04698491301235053</v>
+        <v>-0.0321591706503529</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.7886779214828342</v>
+        <v>0.8553590429456704</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.07692212197636894</v>
+        <v>-0.07255193694871198</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4791,19 +4404,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.01474881982114307</v>
+        <v>-0.02466362643383457</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.01238246152936839</v>
+        <v>-0.02232108134351685</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.1878863304044792</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.103867108384541</v>
+        <v>0.09228250964986333</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.3059568480665255</v>
+        <v>0.2759947934484516</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -4812,89 +4425,27 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.2083486754324957</v>
+        <v>-0.1878863304044792</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.02043384461706754</v>
+        <v>0.04680968554454545</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.9292931988265379</v>
+        <v>0.8380254332546916</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.1878863304044792</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2445519253278838</v>
+        <v>0.2009850468985936</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.0321591706503529</v>
+        <v>-0.06603947961381429</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.8553590429456704</v>
+        <v>0.702976994072228</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.07255193694871198</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>-0.02466362643383457</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-0.02232108134351685</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.09228250964986333</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2759947934484516</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.04680968554454545</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.8380254332546916</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.2009850468985936</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.06603947961381429</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.702976994072228</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.05694989141396378</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_yearly.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -680,27 +681,27 @@
         <v>0.3231577995029844</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -757,27 +758,27 @@
         <v>0.6541746872192167</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -834,27 +835,27 @@
         <v>0.3840428795918789</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -911,27 +912,27 @@
         <v>0.6701720817343015</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -988,27 +989,27 @@
         <v>0.6616703820773265</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1065,27 +1066,27 @@
         <v>0.7090015670332926</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1232,28 +1233,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.09343144196766684</v>
+        <v>0.05644008609220896</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.2715577666208207</v>
+        <v>0.08831268540851259</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.1809616537571159</v>
+        <v>0.2970580221997939</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.4704588408798217</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -1262,10 +1263,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.7119888462278889</v>
+        <v>0.2724034021441999</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -1274,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.1395291740668931</v>
+        <v>-0.08310591627223018</v>
       </c>
     </row>
     <row r="3">
@@ -1294,49 +1295,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.07875802975746682</v>
+        <v>0.06080449145103839</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.1899354110613138</v>
+        <v>0.004131237934158039</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.4083924126510692</v>
+        <v>-0.1750807802290463</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1747566149670305</v>
+        <v>0.09133598046890438</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1695100138228</v>
+        <v>0.3019730837759698</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9844875346260388</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.3826898310425586</v>
+        <v>-0.1732838894298508</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.1657453973607821</v>
+        <v>-0.004282016987886106</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.8134395568523631</v>
+        <v>1.020946587031668</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.4083924126510692</v>
+        <v>-0.1750807802290463</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.7475137848115354</v>
+        <v>0.2831544926824385</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.02075068342993025</v>
+        <v>0.008449435548601558</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.049895358293683</v>
+        <v>1.039467534008799</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.135237664710318</v>
+        <v>-0.08591019594889115</v>
       </c>
     </row>
     <row r="4">
@@ -1356,49 +1357,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.1398808617338245</v>
+        <v>0.05490478870196891</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.05123652188751626</v>
+        <v>-0.001453274454890408</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.3244669395004775</v>
+        <v>0.09909320577935192</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.1800318889201953</v>
+        <v>0.3278361807192359</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.4963092168449624</v>
+        <v>-0.1795337383472572</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.04881655659796225</v>
+        <v>-0.01180949453260038</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.05494715736832</v>
+        <v>1.057769178806841</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1822864687558077</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.7076332683288911</v>
+        <v>0.2857381686566542</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.002544162544396711</v>
+        <v>0.0104799833841871</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.993882519477554</v>
+        <v>1.048952275953571</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.1384848318129372</v>
+        <v>-0.1183724319722919</v>
       </c>
     </row>
     <row r="5">
@@ -1418,49 +1419,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.05511881647811512</v>
       </c>
     </row>
     <row r="6">
@@ -1480,49 +1481,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.0885112574001572</v>
+        <v>0.07356843507801791</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.005427261428731622</v>
+        <v>0.01621327059745248</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2850465641718551</v>
+        <v>0.09749194666774841</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1968916734512504</v>
+        <v>0.3220812091790823</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.5046718081597295</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.06460870262993701</v>
+        <v>-0.01250556989261897</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.072722551490211</v>
+        <v>1.061174210396038</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8401713401642454</v>
+        <v>0.3094081175441943</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.07487343987011807</v>
+        <v>0.02908253415358342</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.180034412920183</v>
+        <v>1.135845276192276</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1423032147182204</v>
+        <v>-0.1018465904642569</v>
       </c>
     </row>
     <row r="7">
@@ -1542,49 +1543,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.1051693667903664</v>
+        <v>0.08494274132399737</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.01294764165236018</v>
+        <v>0.02697990696019525</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.3008863680359475</v>
+        <v>0.09182038001016277</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1971883490136813</v>
+        <v>0.3163123058422522</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5165540962256934</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.08704754021851291</v>
+        <v>-0.007563205902741954</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.097979358321054</v>
+        <v>1.036997366224467</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8509426312718931</v>
+        <v>0.3166911337044074</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.08116512286290178</v>
+        <v>0.0348063605343838</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.195162867761455</v>
+        <v>1.162581418629872</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1452618683874185</v>
+        <v>-0.09650539287730475</v>
       </c>
     </row>
     <row r="8">
@@ -1604,49 +1605,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.02359204792244729</v>
+        <v>0.0817485147145196</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.07703707946457228</v>
+        <v>0.02395633122549046</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.2543247912284557</v>
+        <v>0.0906505688722604</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1824361712833101</v>
+        <v>0.3208155612581201</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.997229916897507</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.4816886905342951</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.0212067550577778</v>
+        <v>-0.005946824936880146</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.023869993883996</v>
+        <v>1.029090423147515</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.8838252884816873</v>
+        <v>0.3106799034324066</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1003724075845553</v>
+        <v>0.03008204884056798</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.241347098573505</v>
+        <v>1.140514035386183</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1388121261286483</v>
+        <v>-0.1021137573160278</v>
       </c>
     </row>
   </sheetData>
@@ -1792,28 +1793,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.0534149946425504</v>
+        <v>-0.09123360655355228</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.2216991067360385</v>
+        <v>0.2716992530341478</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2389480542019929</v>
+        <v>0.1810585772249195</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.5035092528573141</v>
+        <v>-0.4707583434268607</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -1822,10 +1823,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1.121721302370637</v>
+        <v>0.717110477150922</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -1834,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.1530343433756414</v>
+        <v>-0.1395291740668931</v>
       </c>
     </row>
     <row r="3">
@@ -1854,49 +1855,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.07497725807198008</v>
+        <v>0.08253636578618129</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.02046891637112713</v>
+        <v>0.1912152271396397</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.5249389151859554</v>
+        <v>-0.408392412651069</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.2210267815557181</v>
+        <v>0.1748533787187136</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2426740023958808</v>
+        <v>0.169601333103672</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>0.9844703272323905</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.5243350442512886</v>
+        <v>-0.3814207717728257</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.04194598089456325</v>
+        <v>0.1688029854499726</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.041361288349305</v>
+        <v>0.8102262596054978</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.5249389151859554</v>
+        <v>-0.408392412651069</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1.259946302707822</v>
+        <v>0.7500367234908474</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.065147576254593</v>
+        <v>0.01917538025541465</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.123225795966486</v>
+        <v>1.045915165639109</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.1542125880460703</v>
+        <v>-0.135237664710318</v>
       </c>
     </row>
     <row r="4">
@@ -1916,49 +1917,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.1991773958883538</v>
+        <v>-0.1430381740072413</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.1383712990484478</v>
+        <v>-0.057005373248039</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.4884434813691406</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2057028412243141</v>
+        <v>0.3246257835002017</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2187686648988483</v>
+        <v>0.1801113732573058</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9636627906976745</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.4884434813691407</v>
+        <v>-0.4996173751341991</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.03034451613625655</v>
+        <v>-0.05452902534959503</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.9700784615125182</v>
+        <v>1.061303282480902</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.4884434813691406</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.344173815041704</v>
+        <v>0.7126130752893149</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.1048453029257503</v>
+        <v>-0.002619168609971578</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.198313531356619</v>
+        <v>0.9937284393340964</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.1220563520675992</v>
+        <v>-0.1384848318129372</v>
       </c>
     </row>
     <row r="5">
@@ -1978,49 +1979,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.1975871140978549</v>
+        <v>0.2834444878548723</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1368616548924535</v>
+        <v>0.412293078958915</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1847647558521955</v>
+        <v>0.1114874581688012</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2118271660599822</v>
+        <v>0.1527921426208967</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9614825581395349</v>
+        <v>0.9584026622296173</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2500855498878848</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07708757922255405</v>
+        <v>0.4169603635659389</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.9239869583598836</v>
+        <v>0.5312397610786888</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.239468393809461</v>
+        <v>0.711454536798154</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.05549602170052359</v>
+        <v>-0.003293870969882207</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.104970005642202</v>
+        <v>0.9921128744691625</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
     </row>
     <row r="6">
@@ -2040,49 +2041,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1019213862233868</v>
+        <v>-0.08568579969177081</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.04604680190383625</v>
+        <v>0.006104766749507107</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2007330591320373</v>
+        <v>0.2851956016709155</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2406643520933329</v>
+        <v>0.1969993142200973</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9738372093023255</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.5031043706109168</v>
+        <v>-0.5038864433233314</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0008154879999826559</v>
+        <v>-0.06259541267211743</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9991958792334011</v>
+        <v>1.070371774306359</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.217611347433591</v>
+        <v>0.8429534690262739</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.04519445836539138</v>
+        <v>0.07328765012496707</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.085484732134711</v>
+        <v>1.175486198968011</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1903416370175206</v>
+        <v>-0.1423032147182204</v>
       </c>
     </row>
     <row r="7">
@@ -2102,49 +2103,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.0368407257795742</v>
+        <v>-0.1038483060444678</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.01573384558532909</v>
+        <v>-0.01388112454629287</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2138025395451635</v>
+        <v>0.3010407489256601</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2486051666650726</v>
+        <v>0.1972971759393627</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9898255813953488</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.5129198176356869</v>
+        <v>-0.5164822477237525</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.01895415943304257</v>
+        <v>-0.08639513486703954</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.018689954007736</v>
+        <v>1.097128186755113</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.128685919321732</v>
+        <v>0.8533997764026979</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.003282531472589278</v>
+        <v>0.07937130491330469</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.006208865728391</v>
+        <v>1.190053420768935</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.204891821182839</v>
+        <v>-0.1452618683874185</v>
       </c>
     </row>
     <row r="8">
@@ -2164,49 +2165,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.1822704228151848</v>
+        <v>-0.01931799600343886</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1223216195212393</v>
+        <v>0.07913542035525478</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.4718154607749649</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1693242986572223</v>
+        <v>0.2544644086576291</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2376559716880013</v>
+        <v>0.1825337474969582</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9636627906976745</v>
+        <v>0.9972268441486412</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.4706028507084905</v>
+        <v>-0.4804657787516077</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.06627797665555812</v>
+        <v>-0.01834216034240954</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.9346458839393986</v>
+        <v>1.020620846046152</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.4718154607749649</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.233239118112769</v>
+        <v>0.8876177235064009</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.05256006791162027</v>
+        <v>0.09929893773543874</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.099416687109758</v>
+        <v>1.237769844101154</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1671095976979867</v>
+        <v>-0.1388121261286483</v>
       </c>
     </row>
   </sheetData>
@@ -2352,28 +2353,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.0534149946425504</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.08126757478702552</v>
+        <v>0.2216991067360385</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2145128387962864</v>
+        <v>0.2389480542019929</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573141</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -2382,10 +2383,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.121721302370637</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -2394,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756414</v>
       </c>
     </row>
     <row r="3">
@@ -2414,49 +2415,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02371638245312702</v>
+        <v>0.07497725807198008</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.0002995005432211428</v>
+        <v>0.02046891637112713</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.1720264251314347</v>
+        <v>-0.5249389151859554</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.05917775215329362</v>
+        <v>0.2210267815557181</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1871340905199546</v>
+        <v>0.2426740023958808</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.1706425815157273</v>
+        <v>-0.5243350442512886</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.03081708185076937</v>
+        <v>-0.04194598089456325</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.8731340307936648</v>
+        <v>1.041361288349305</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.1720264251314347</v>
+        <v>-0.5249389151859554</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.2343488580883055</v>
+        <v>1.259946302707822</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.02960523437655505</v>
+        <v>0.065147576254593</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.8615547616447651</v>
+        <v>1.123225795966486</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02614394426954258</v>
+        <v>-0.1542125880460703</v>
       </c>
     </row>
     <row r="4">
@@ -2476,49 +2477,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.007859810079828833</v>
+        <v>0.1991773958883538</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.01519436250049544</v>
+        <v>0.1383712990484478</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.2057028412243141</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2200814955608064</v>
+        <v>0.2187686648988483</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9636627906976745</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4884434813691407</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.004612638980404427</v>
+        <v>0.03034451613625655</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.9810109562715352</v>
+        <v>0.9700784615125182</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2469279583475472</v>
+        <v>1.344173815041704</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.01971605842128599</v>
+        <v>0.1048453029257503</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.9078002770441739</v>
+        <v>1.198313531356619</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.03283823265868402</v>
+        <v>-0.1220563520675992</v>
       </c>
     </row>
     <row r="5">
@@ -2538,49 +2539,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>0.1975871140978549</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>0.1368616548924535</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.1847647558521955</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.2118271660599822</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9614825581395349</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.07708757922255405</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.9239869583598836</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>1.239468393809461</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>0.05549602170052359</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>1.104970005642202</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.1247701957278803</v>
       </c>
     </row>
     <row r="6">
@@ -2600,49 +2601,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.05429070103913802</v>
+        <v>0.1019213862233868</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.03017445041727607</v>
+        <v>0.04604680190383625</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.05847802996069337</v>
+        <v>0.2007330591320373</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1943365262252255</v>
+        <v>0.2406643520933329</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.9738372093023255</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.5031043706109168</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0327416689383877</v>
+        <v>0.0008154879999826559</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.8652110026700077</v>
+        <v>0.9991958792334011</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2688449302478968</v>
+        <v>1.217611347433591</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.002485828352167374</v>
+        <v>0.04519445836539138</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9883753293641022</v>
+        <v>1.085484732134711</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02892173456683256</v>
+        <v>-0.1903416370175206</v>
       </c>
     </row>
     <row r="7">
@@ -2662,49 +2663,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.05350828208151159</v>
+        <v>0.0368407257795742</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.02940992881154214</v>
+        <v>-0.01573384558532909</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.06099826392968127</v>
+        <v>0.2138025395451635</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1970235800584944</v>
+        <v>0.2486051666650726</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>0.9898255813953488</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.5129198176356869</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.02467166685502487</v>
+        <v>-0.01895415943304257</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.8984331176243276</v>
+        <v>1.018689954007736</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2778889047779733</v>
+        <v>1.128685919321732</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.004624175830937105</v>
+        <v>0.003282531472589278</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.021624389692979</v>
+        <v>1.006208865728391</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02931693909409494</v>
+        <v>-0.204891821182839</v>
       </c>
     </row>
     <row r="8">
@@ -2724,49 +2725,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.03061996343987849</v>
+        <v>0.1822704228151848</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.007045166365681865</v>
+        <v>0.1223216195212393</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.05187138456619264</v>
+        <v>0.1693242986572223</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1829382024919134</v>
+        <v>0.2376559716880013</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.903448275862069</v>
+        <v>0.9636627906976745</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4706028507084905</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.03960193338246176</v>
+        <v>0.06627797665555812</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.8369690652301233</v>
+        <v>0.9346458839393986</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2321720269664671</v>
+        <v>1.233239118112769</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.03131657028652601</v>
+        <v>0.05256006791162027</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.8535519096845917</v>
+        <v>1.099416687109758</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02321227998309094</v>
+        <v>-0.1671095976979867</v>
       </c>
     </row>
   </sheetData>
@@ -2912,28 +2913,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.01891210187562642</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1130717188570336</v>
+        <v>0.08099293800751969</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886579</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -2942,10 +2943,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -2954,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.05185156587886031</v>
+        <v>-0.03286068493604632</v>
       </c>
     </row>
     <row r="3">
@@ -2974,49 +2975,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02030574172231736</v>
+        <v>0.02187096031419999</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.07061291773020784</v>
+        <v>0.002903938851179566</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1721376387087035</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1238192782772627</v>
+        <v>0.05908049496517706</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.4534531218343514</v>
+        <v>0.1865055692046844</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9754098360655737</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1721376387087035</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.01981061610580925</v>
+        <v>0.03350097751902914</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.048450159778007</v>
+        <v>0.8651313704437881</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1721376387087035</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.4665482057250212</v>
+        <v>0.2343488580883055</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.05182906738141368</v>
+        <v>-0.02960523437655505</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.8533696793512648</v>
+        <v>0.8615547616447651</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.0648814235732682</v>
+        <v>-0.02614394426954258</v>
       </c>
     </row>
     <row r="4">
@@ -3036,49 +3037,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.06404560575472296</v>
+        <v>0.005589722741125236</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.03077067932102873</v>
+        <v>-0.01307510148321644</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1160654159706605</v>
+        <v>0.07558961362210245</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.4686838807519479</v>
+        <v>0.2193422573785161</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.02087621099141768</v>
+        <v>0.00677452384599353</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.051056249472068</v>
+        <v>0.9727270421740364</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.5310826913419402</v>
+        <v>0.2469279583475472</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.01010543144869347</v>
+        <v>-0.01971605842128599</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.9714105862119542</v>
+        <v>0.9078002770441739</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.06450069847101803</v>
+        <v>-0.03283823265868402</v>
       </c>
     </row>
     <row r="5">
@@ -3098,49 +3099,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.01712918805183983</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.001749821030199383</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.04617799198161064</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.167065999353103</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.02330447460112972</v>
       </c>
     </row>
     <row r="6">
@@ -3160,49 +3161,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.03488923518577902</v>
+        <v>0.05158957805580444</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.05732894814631817</v>
+        <v>0.03207094716023584</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1241006863166954</v>
+        <v>0.05828083851341805</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4729976975805062</v>
+        <v>0.1937034912863763</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.02953137989967969</v>
+        <v>0.03464289179502811</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.072223905958428</v>
+        <v>0.8605342385127216</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.502409700880692</v>
+        <v>0.2688449302478968</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.02864344881523828</v>
+        <v>-0.002485828352167374</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9189644287180407</v>
+        <v>0.9883753293641022</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.06316869981712403</v>
+        <v>-0.02892173456683256</v>
       </c>
     </row>
     <row r="7">
@@ -3222,49 +3223,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03395357056649728</v>
+        <v>0.05021558177844221</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.05818123641143114</v>
+        <v>0.03072245372804194</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1251027258735238</v>
+        <v>0.06079370905413644</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4741154654082622</v>
+        <v>0.1963965378157337</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.8904109589041096</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3121003427249628</v>
+        <v>-0.1781636276426457</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.03082746164398775</v>
+        <v>0.02597815036206796</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.075393689637123</v>
+        <v>0.8954168565455383</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.5030587086818397</v>
+        <v>0.2778889047779733</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.02822384424329949</v>
+        <v>0.004624175830937105</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9201515377292117</v>
+        <v>1.021624389692979</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.06371665664689741</v>
+        <v>-0.02931693909409494</v>
       </c>
     </row>
     <row r="8">
@@ -3284,49 +3285,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.04515891089417345</v>
+        <v>0.03014589372818866</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.04797439533710812</v>
+        <v>0.0110252806222273</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1195047161892575</v>
+        <v>0.05169621954656301</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4584419203783911</v>
+        <v>0.1823084026644021</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.01649499533326504</v>
+        <v>0.0437107207679579</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.040341257190876</v>
+        <v>0.824028865917714</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.4972066941042887</v>
+        <v>0.2321720269664671</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.03200736127876636</v>
+        <v>-0.03131657028652601</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.9094475381374805</v>
+        <v>0.8535519096845917</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.06227097997115527</v>
+        <v>-0.02321227998309094</v>
       </c>
     </row>
   </sheetData>
@@ -3472,28 +3473,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363057</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1799741913752893</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2405796270435321</v>
+        <v>0.4518304992174231</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.3098313187450099</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -3502,10 +3503,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.5373300241682997</v>
+        <v>0.5657770181230004</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -3514,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.1055402030174769</v>
+        <v>-0.05185156587886031</v>
       </c>
     </row>
     <row r="3">
@@ -3534,49 +3535,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1586899770747519</v>
+        <v>0.02478007296034423</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.09205595987520399</v>
+        <v>-0.07790267044829702</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.2880125431936822</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1436360562266181</v>
+        <v>0.1218539540374459</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2057466595818524</v>
+        <v>0.446190328085488</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9317738791423001</v>
+        <v>0.9603174603174603</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.2880125431936822</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.03161368538435094</v>
+        <v>-0.01981061610580925</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.9295785344112211</v>
+        <v>1.048450159778007</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.2880125431936822</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.6274022330002238</v>
+        <v>0.4729794372477125</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.05859002778577316</v>
+        <v>-0.05926615335466501</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.167629212552084</v>
+        <v>0.835982060241419</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.09441700987711088</v>
+        <v>-0.0648814235732682</v>
       </c>
     </row>
     <row r="4">
@@ -3596,49 +3597,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.07593530609125765</v>
+        <v>0.07322454526542055</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.1290764775225159</v>
+        <v>-0.0343123238727534</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1908003349426301</v>
+        <v>0.1142230623487696</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.1967758842540266</v>
+        <v>0.4612108270599598</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.2809671323736413</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.04182193013870528</v>
+        <v>-0.02087621099141768</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.9068390294167656</v>
+        <v>1.051056249472068</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.2809671323736415</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2851494493697155</v>
+        <v>0.5442905043658335</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.164038021006592</v>
+        <v>-0.01372258853493979</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.530678422094654</v>
+        <v>0.9620230001062083</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.1279869945573349</v>
+        <v>-0.06450069847101803</v>
       </c>
     </row>
     <row r="5">
@@ -3658,49 +3659,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.09480060127513035</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.03184073837926271</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1155318330023982</v>
+        <v>0.1158491063192834</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1720647483703307</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4372788934221374</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.06508110111248899</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.813799478447114</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.07121447292125116</v>
       </c>
     </row>
     <row r="6">
@@ -3720,49 +3721,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3595704026356366</v>
+        <v>0.04240795586410551</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.2813841410940174</v>
+        <v>-0.06204109762882104</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1392666701512926</v>
+        <v>0.1221307783139223</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2294212443587999</v>
+        <v>0.4654425791584146</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9122807017543859</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.02227482471563635</v>
+        <v>-0.02953137989967969</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9503814318660629</v>
+        <v>1.072223905958428</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9269870146170396</v>
+        <v>0.5133250708558199</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.2534634621863614</v>
+        <v>-0.03349898910258509</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.725172562340744</v>
+        <v>0.9072921918228616</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.111586064624036</v>
+        <v>-0.06316869981712403</v>
       </c>
     </row>
     <row r="7">
@@ -3782,49 +3783,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.2930599188275502</v>
+        <v>0.04161196027515435</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.2186985464363551</v>
+        <v>-0.06275733463056765</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1617038815488626</v>
+        <v>0.1231169123948052</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.244271120885344</v>
+        <v>0.466550204870466</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9317738791423001</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3268135676014445</v>
+        <v>-0.3121003427249628</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.02460593955894141</v>
+        <v>-0.03082746164398775</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.054811272550568</v>
+        <v>1.075393689637123</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9208050795385059</v>
+        <v>0.5141917127874007</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.2494422468446016</v>
+        <v>-0.0329454990963135</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.713667649530219</v>
+        <v>0.9088239647719573</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1128970535188779</v>
+        <v>-0.06371665664689741</v>
       </c>
     </row>
     <row r="8">
@@ -3844,49 +3845,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.265288122701582</v>
+        <v>0.05462537085906805</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1925238525356017</v>
+        <v>-0.05104786499468505</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1660049019432621</v>
+        <v>0.1176077422857334</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2482386617226885</v>
+        <v>0.4511654067224259</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3240432642895691</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.02059198849579269</v>
+        <v>-0.01649499533326504</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.045869944982081</v>
+        <v>1.040341257190876</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.8718477912225604</v>
+        <v>0.5107675479430458</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.2175965874570334</v>
+        <v>-0.03513237807379377</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.622555509664736</v>
+        <v>0.9027718192540731</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.11030602040881</v>
+        <v>-0.06227097997115527</v>
       </c>
     </row>
   </sheetData>
@@ -4032,25 +4033,585 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.002396027003974677</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.1799741913752893</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.2405796270435321</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.9746588693957114</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>-0.3098313187450099</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>-0.3098313187450098</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.5373300241682997</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>-0.1055402030174769</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>equal_weight</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>equal_t_10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.1586899770747519</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.09205595987520399</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-0.2880125431936822</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.1436360562266181</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.2057466595818524</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.9317738791423001</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.2880125431936822</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.03161368538435094</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.9295785344112211</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>-0.2880125431936822</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.6274022330002238</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.05859002778577316</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>1.167629212552084</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>-0.09441700987711088</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.07593530609125765</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>-0.1290764775225159</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1908003349426301</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.1967758842540266</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.2809671323736413</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.04182193013870528</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.9068390294167656</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>-0.2809671323736415</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.2851494493697155</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>-0.164038021006592</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.530678422094654</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>-0.1279869945573349</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.09480060127513035</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.03184073837926271</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.1155318330023982</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.1720647483703307</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.1036687135184475</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.769071443176754</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.4372788934221374</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>-0.06508110111248899</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.813799478447114</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>-0.08016850348153992</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.3595704026356366</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.2813841410940174</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.1392666701512926</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.2294212443587999</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.9122807017543859</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0.02227482471563635</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.9503814318660629</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.9269870146170396</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.2534634621863614</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1.725172562340744</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>-0.111586064624036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.2930599188275502</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.2186985464363551</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.1617038815488626</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.244271120885344</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.9317738791423001</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.3268135676014445</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.02460593955894141</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>1.054811272550568</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.9208050795385059</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.2494422468446016</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1.713667649530219</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>-0.1128970535188779</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.265288122701582</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.1925238525356017</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1660049019432621</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2482386617226885</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.3240432642895691</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.02059198849579269</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.045869944982081</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.8718477912225604</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.2175965874570334</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.622555509664736</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.11030602040881</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>-0.2242012270138071</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.103821015825279</v>
+        <v>0.1032426212645815</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.3353086213005</v>
+        <v>0.3336266559947871</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>0.9887640449438202</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>-0.2242012270138072</v>
@@ -4065,7 +4626,7 @@
         <v>-0.2242012270138071</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.2859055823922785</v>
+        <v>0.2953423679490124</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -4094,19 +4655,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.02029792505039962</v>
+        <v>-0.01607749906234435</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.01794489449822623</v>
+        <v>-0.02089958783342205</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>-0.1844872203105785</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.08787989515899092</v>
+        <v>0.08740674062405762</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2733839717261059</v>
+        <v>0.2719331495891807</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -4127,13 +4688,13 @@
         <v>-0.1844872203105785</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.2013325840493982</v>
+        <v>0.2065077647371401</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.0657692131529144</v>
+        <v>-0.06858001823296267</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.7041925602318554</v>
+        <v>0.6992148338595002</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>-0.06150746577529342</v>
@@ -4156,22 +4717,22 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.002943983606027434</v>
+        <v>0.002465108212122091</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.00535283614996529</v>
+        <v>-0.002447855702312429</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>-0.2112316646811809</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.09716721907930907</v>
+        <v>0.0966259064202601</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.3134216093716399</v>
+        <v>0.31163690291174</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.9775280898876404</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -4189,13 +4750,13 @@
         <v>-0.2112316646811809</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2715317523498695</v>
+        <v>0.2709246344263136</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.01117798245783186</v>
+        <v>-0.01885040907089353</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.9497252557220541</v>
+        <v>0.9173239732170286</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>-0.04769139338712791</v>
@@ -4218,19 +4779,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.02335558522365555</v>
+        <v>-0.02027479846139824</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.02100989850384682</v>
+        <v>-0.02507631676042987</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>-0.1556116196127491</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.07028481312061448</v>
+        <v>0.06992591782126945</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.2355679791479366</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4251,13 +4812,13 @@
         <v>-0.1556116196127491</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.1602779293212004</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.1042692974226319</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.5426851908659128</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>-0.04423229897254077</v>
@@ -4280,19 +4841,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.02506240001890081</v>
+        <v>-0.02078840693949269</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.02272081269569726</v>
+        <v>-0.02558740810361515</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>-0.2044491165694975</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1047999997493329</v>
+        <v>0.1042391861264295</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.3040021784991731</v>
+        <v>0.3023717680461677</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4313,13 +4874,13 @@
         <v>-0.2044491165694975</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2254874204614814</v>
+        <v>0.2308597896818865</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.04698491301235053</v>
+        <v>-0.04978033596571441</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7886779214828342</v>
+        <v>0.7816683779068971</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>-0.07692212197636894</v>
@@ -4342,19 +4903,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.01474881982114307</v>
+        <v>-0.01147991081539435</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.01238246152936839</v>
+        <v>-0.01632453182721105</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>-0.2083486754324958</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.103867108384541</v>
+        <v>0.103295545269285</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3059568480665255</v>
+        <v>0.304269882301803</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -4375,13 +4936,13 @@
         <v>-0.2083486754324958</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2445519253278838</v>
+        <v>0.2486811535680242</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.0321591706503529</v>
+        <v>-0.03602230231600423</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8553590429456704</v>
+        <v>0.8420097505649996</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>-0.07255193694871198</v>
@@ -4404,19 +4965,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.02466362643383457</v>
+        <v>-0.02221658291291773</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.02232108134351685</v>
+        <v>-0.02700858475410772</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>-0.1878863304044792</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.09228250964986333</v>
+        <v>0.09179827266736014</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2759947934484516</v>
+        <v>0.274462303017576</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -4437,13 +4998,13 @@
         <v>-0.1878863304044792</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2009850468985936</v>
+        <v>0.203998225487418</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.06603947961381429</v>
+        <v>-0.07051737418750892</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.702976994072228</v>
+        <v>0.6907177825656089</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>-0.05694989141396378</v>
